--- a/data/trans_orig/P36BPD12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen frutos secos a la semana en 2023</t>
+          <t>Población según el número de veces que consumen frutos secos a la semana en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205560</t>
+          <t>204719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>246530</t>
+          <t>245618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>339862</t>
+          <t>340421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>383327</t>
+          <t>381280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>560961</t>
+          <t>558991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>620888</t>
+          <t>619809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174896</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215316</t>
+          <t>216596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272090</t>
+          <t>272711</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315062</t>
+          <t>314101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463118</t>
+          <t>460058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519165</t>
+          <t>519445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77486</t>
+          <t>77304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108674</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>85322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119261</t>
+          <t>116960</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170488</t>
+          <t>170637</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216438</t>
+          <t>216204</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423424</t>
+          <t>421909</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>719563</t>
+          <t>721083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511363</t>
+          <t>510205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>800996</t>
+          <t>797825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1072977</t>
+          <t>1055334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1478280</t>
+          <t>1473093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1047238</t>
+          <t>1048146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1526575</t>
+          <t>1567993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>921694</t>
+          <t>922524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1414319</t>
+          <t>1383917</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2025993</t>
+          <t>2014412</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2710328</t>
+          <t>2692956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330499</t>
+          <t>321554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>543806</t>
+          <t>539366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>347602</t>
+          <t>351476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>651162</t>
+          <t>651124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>764540</t>
+          <t>776328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1119917</t>
+          <t>1124314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187029</t>
+          <t>185697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244742</t>
+          <t>240453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>209682</t>
+          <t>207516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>251841</t>
+          <t>253914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>407917</t>
+          <t>408874</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>480689</t>
+          <t>480816</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275904</t>
+          <t>276731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>331158</t>
+          <t>332029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248693</t>
+          <t>246540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291991</t>
+          <t>291741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>538962</t>
+          <t>539234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>608249</t>
+          <t>606638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109749</t>
+          <t>109347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153887</t>
+          <t>153359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138521</t>
+          <t>139302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177762</t>
+          <t>179031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258567</t>
+          <t>259966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316599</t>
+          <t>318767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>811475</t>
+          <t>795665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1166065</t>
+          <t>1164003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1067275</t>
+          <t>1057254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1395827</t>
+          <t>1396012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2049417</t>
+          <t>2023204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2513990</t>
+          <t>2517989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1538550</t>
+          <t>1538321</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2099240</t>
+          <t>2095753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1472555</t>
+          <t>1480663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1966699</t>
+          <t>2010387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3078556</t>
+          <t>3061771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3809378</t>
+          <t>3809669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>530954</t>
+          <t>547536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>771098</t>
+          <t>767788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>616993</t>
+          <t>614729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>913738</t>
+          <t>917902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1240982</t>
+          <t>1244663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1613583</t>
+          <t>1608796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>225298</t>
+          <t>248232</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204719</t>
+          <t>225335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245618</t>
+          <t>270079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>361319</t>
+          <t>391118</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340421</t>
+          <t>369486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>381280</t>
+          <t>412715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>586617</t>
+          <t>639350</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558991</t>
+          <t>609345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>619809</t>
+          <t>671189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>195120</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174453</t>
+          <t>198658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>216596</t>
+          <t>243660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>294100</t>
+          <t>322510</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272711</t>
+          <t>301401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314101</t>
+          <t>345699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>489220</t>
+          <t>543322</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460058</t>
+          <t>513885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>519445</t>
+          <t>576739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92113</t>
+          <t>107062</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77304</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109643</t>
+          <t>126137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99321</t>
+          <t>107628</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116960</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>191434</t>
+          <t>214690</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>170637</t>
+          <t>192670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>239808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>512531</t>
+          <t>576107</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512531</t>
+          <t>576107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>512531</t>
+          <t>576107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754740</t>
+          <t>821256</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754740</t>
+          <t>821256</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754740</t>
+          <t>821256</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267271</t>
+          <t>1397363</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267271</t>
+          <t>1397363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267271</t>
+          <t>1397363</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>625421</t>
+          <t>678316</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421909</t>
+          <t>630189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>721083</t>
+          <t>731009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>694354</t>
+          <t>764668</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510205</t>
+          <t>722714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>797825</t>
+          <t>804021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1319775</t>
+          <t>1442983</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1055334</t>
+          <t>1377512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1473093</t>
+          <t>1507179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1194947</t>
+          <t>1046190</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1048146</t>
+          <t>987088</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1567993</t>
+          <t>1097417</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1066547</t>
+          <t>974314</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>922524</t>
+          <t>932710</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1383917</t>
+          <t>1019221</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2261495</t>
+          <t>2020504</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2014412</t>
+          <t>1954972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2692956</t>
+          <t>2089360</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>466238</t>
+          <t>502173</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>321554</t>
+          <t>456022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>539366</t>
+          <t>554084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>473806</t>
+          <t>429240</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>351476</t>
+          <t>394937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>651124</t>
+          <t>465970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>940044</t>
+          <t>931413</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>776328</t>
+          <t>869824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1124314</t>
+          <t>990435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2286606</t>
+          <t>2226679</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2286606</t>
+          <t>2226679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2286606</t>
+          <t>2226679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234708</t>
+          <t>2168221</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2234708</t>
+          <t>2168221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2234708</t>
+          <t>2168221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4521314</t>
+          <t>4394900</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4521314</t>
+          <t>4394900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4521314</t>
+          <t>4394900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>212773</t>
+          <t>216392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185697</t>
+          <t>190057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>244113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231027</t>
+          <t>252523</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>207516</t>
+          <t>229563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253914</t>
+          <t>276101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>443801</t>
+          <t>468915</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>408874</t>
+          <t>434023</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>480816</t>
+          <t>503490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>302394</t>
+          <t>332723</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>276731</t>
+          <t>303921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>332029</t>
+          <t>360790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>270587</t>
+          <t>300614</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>246540</t>
+          <t>276125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291741</t>
+          <t>323502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>572982</t>
+          <t>633337</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>539234</t>
+          <t>595506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>606638</t>
+          <t>668921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,29%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130829</t>
+          <t>161860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109347</t>
+          <t>137192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153359</t>
+          <t>186114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>158129</t>
+          <t>181002</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139302</t>
+          <t>162747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179031</t>
+          <t>202039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>288958</t>
+          <t>342861</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259966</t>
+          <t>312792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318767</t>
+          <t>377493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>659743</t>
+          <t>734139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>659743</t>
+          <t>734139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>659743</t>
+          <t>734139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305740</t>
+          <t>1445114</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305740</t>
+          <t>1445114</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305740</t>
+          <t>1445114</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1063493</t>
+          <t>1142940</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>795665</t>
+          <t>1084548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1164003</t>
+          <t>1205795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>32,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>30,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,1%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1286700</t>
+          <t>1408309</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1057254</t>
+          <t>1355645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1396012</t>
+          <t>1466395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2350193</t>
+          <t>2551249</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2023204</t>
+          <t>2476708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2517989</t>
+          <t>2631038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1692462</t>
+          <t>1599726</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1538321</t>
+          <t>1527550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2095753</t>
+          <t>1657905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1631235</t>
+          <t>1597438</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1480663</t>
+          <t>1538047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2010387</t>
+          <t>1650258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3323696</t>
+          <t>3197163</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3061771</t>
+          <t>3114668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3809669</t>
+          <t>3282783</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>689180</t>
+          <t>771094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>547536</t>
+          <t>718298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>767788</t>
+          <t>832893</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>731256</t>
+          <t>717870</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>614729</t>
+          <t>678082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>917902</t>
+          <t>771070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1420435</t>
+          <t>1488965</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1244663</t>
+          <t>1422367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1608796</t>
+          <t>1573760</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3445134</t>
+          <t>3513760</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3445134</t>
+          <t>3513760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3445134</t>
+          <t>3513760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3649191</t>
+          <t>3723617</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3649191</t>
+          <t>3723617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3649191</t>
+          <t>3723617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7094325</t>
+          <t>7237377</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7094325</t>
+          <t>7237377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7094325</t>
+          <t>7237377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
